--- a/AmLaw200_2025 Rank_gross revenue_with_websites_source_failure_report.xlsx
+++ b/AmLaw200_2025 Rank_gross revenue_with_websites_source_failure_report.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-12T20:57:27.464258</t>
+          <t>2026-04-15T08:50:45.595871</t>
         </is>
       </c>
     </row>
